--- a/www/download/IND.labour_force_value.s.mv.zdW16.xlsx
+++ b/www/download/IND.labour_force_value.s.mv.zdW16.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7764.503</t>
+          <t>6843913050.21835</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7503.799</t>
+          <t>6661491877.29695</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8457.233</t>
+          <t>7488166954.958</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>10040.125</t>
+          <t>8902857028.47447</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>11367.001</t>
+          <t>10091648700.4429</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>12068.206</t>
+          <t>10630843826.0595</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>11916.569</t>
+          <t>10456998325.0189</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>12531.276</t>
+          <t>11048058417.9301</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>11151.936</t>
+          <t>9716456774.68953</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>11692.191</t>
+          <t>10170532699.2867</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12504.397</t>
+          <t>10897522031.332</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>14349.03</t>
+          <t>12453990554.1947</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>13906.06</t>
+          <t>12035822703.2128</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>14096.14</t>
+          <t>12296014641.8406</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>12226.764</t>
+          <t>12226764342.0043</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3027.425</t>
+          <t>2549682660.04977</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2946.77</t>
+          <t>2491901332.91315</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2900.745</t>
+          <t>2450361444.07766</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>3078.537</t>
+          <t>2595528636.98474</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>3121.276</t>
+          <t>2648811113.18915</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>3058.965</t>
+          <t>2607161605.47632</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>3182.359</t>
+          <t>2712223411.12113</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>3182.3</t>
+          <t>2732776698.48403</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>3209.638</t>
+          <t>2744643680.89551</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>3123.117</t>
+          <t>2634468229.116</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>3003.913</t>
+          <t>2555475451.70569</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>3114.545</t>
+          <t>2641112525.48032</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>3196.144</t>
+          <t>2719287955.42348</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>3455.526</t>
+          <t>2964304806.68453</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2959.01</t>
+          <t>2959010294.98133</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7163.601</t>
+          <t>6323438676.76068</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>7350.318</t>
+          <t>6525601410.86441</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>7636.713</t>
+          <t>6758446507.88281</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>8634.043</t>
+          <t>7655082694.36288</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>9440.116</t>
+          <t>8420635386.03747</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>9177.247</t>
+          <t>8148435522.95173</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>8761.701</t>
+          <t>7764940109.69111</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>8647.729</t>
+          <t>7712021615.17368</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>8564.086</t>
+          <t>7598027223.93953</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>7829.196</t>
+          <t>6906507918.36992</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>5885.795</t>
+          <t>5168672544.26916</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>6092.621</t>
+          <t>5336931030.93052</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>5769.386</t>
+          <t>5046717478.78526</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>6140.795</t>
+          <t>5399961122.63479</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>5687.285</t>
+          <t>5687285244.76614</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1361.278</t>
+          <t>1190076721.97401</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1337.909</t>
+          <t>1172907064.40665</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1306.408</t>
+          <t>1147082054.43752</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1312.467</t>
+          <t>1150180613.17112</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1274.69</t>
+          <t>1130950898.55741</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1243.401</t>
+          <t>1096342509.27454</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1310.306</t>
+          <t>1152012341.19541</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>1249.538</t>
+          <t>1104585756.99921</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1282.109</t>
+          <t>1132559181.30057</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1378.897</t>
+          <t>1198168015.51569</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1216.608</t>
+          <t>1066615579.87233</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1143.576</t>
+          <t>1003780975.87749</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1164.707</t>
+          <t>1019815532.32808</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1202.703</t>
+          <t>1054865179.56816</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>1230.186</t>
+          <t>1230186217.99206</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>35826.052</t>
+          <t>32258197479.4402</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>33691.691</t>
+          <t>30187019125.0107</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>34289.44</t>
+          <t>30554667866.548</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>34877.084</t>
+          <t>30975231594.4169</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>36012.595</t>
+          <t>32194405855.6949</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>38249.016</t>
+          <t>34104042140.9031</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>39156.271</t>
+          <t>35048040464.4393</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>40126.535</t>
+          <t>36128288004.7921</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>42223.399</t>
+          <t>37774199933.4172</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>43389.734</t>
+          <t>38405208311.453</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>45426.496</t>
+          <t>40277212529.6407</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>46083.629</t>
+          <t>40864301389.457</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>45783.831</t>
+          <t>40448067862.7557</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>46489.779</t>
+          <t>41162061023.9373</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>41894.644</t>
+          <t>41894644026.657</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>13800.011</t>
+          <t>12404389775.1503</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>14087.423</t>
+          <t>12738469595.7964</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14955.311</t>
+          <t>13493544073.2519</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>16222.366</t>
+          <t>14651290875.8472</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>17367.914</t>
+          <t>15739068260.5644</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>18101.283</t>
+          <t>16299058912.5013</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>18751.059</t>
+          <t>16826578280.6131</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>18168.951</t>
+          <t>16365358142.3828</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>17520.912</t>
+          <t>15683121296.0907</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>16533.468</t>
+          <t>14667509303.5514</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>16185.977</t>
+          <t>14406327976.3502</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>17363.821</t>
+          <t>15410081450.785</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>17599.951</t>
+          <t>15575218994.676</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>17535.246</t>
+          <t>15586427489.6652</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>15336.919</t>
+          <t>15336919002.6377</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>502613.91</t>
+          <t>459402381013.207</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>509149.185</t>
+          <t>468867323916.257</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>527058.424</t>
+          <t>487444975850.884</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>510059.107</t>
+          <t>473078315806.158</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>508734.913</t>
+          <t>472763870541.989</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>490159.689</t>
+          <t>454477761525.934</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>499655.154</t>
+          <t>465190228292.245</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>484670.881</t>
+          <t>454493009948.474</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>534315.695</t>
+          <t>497256419610.902</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>570917.195</t>
+          <t>527731952185.948</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>568982.504</t>
+          <t>527850196630.269</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>603629.121</t>
+          <t>556146892408.826</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>640766.772</t>
+          <t>586864795480.236</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>623564.781</t>
+          <t>569731567947.354</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>571300.313</t>
+          <t>571300313494.568</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>253.945</t>
+          <t>222122990.739828</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>283.639</t>
+          <t>250458649.224782</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>343.046</t>
+          <t>301108975.96302</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>397.968</t>
+          <t>352109418.270019</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>393.254</t>
+          <t>349414554.489562</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>384.272</t>
+          <t>340046290.430523</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>359.05</t>
+          <t>316196572.052213</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>353.06</t>
+          <t>312067100.091675</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>415.609</t>
+          <t>366383176.471502</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>367.623</t>
+          <t>319158399.837342</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>369.801</t>
+          <t>322236964.915533</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>359.275</t>
+          <t>314054712.103201</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>325.3</t>
+          <t>283440222.647658</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>316.624</t>
+          <t>276785841.443381</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>269.754</t>
+          <t>269753633.016423</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1639.897</t>
+          <t>1387753272.10883</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1642.68</t>
+          <t>1387578585.03964</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1757.676</t>
+          <t>1463068371.48028</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1876.254</t>
+          <t>1574790867.97548</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1927.784</t>
+          <t>1642334310.58446</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2046.723</t>
+          <t>1746688626.03942</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2030.977</t>
+          <t>1729821382.65352</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2074.855</t>
+          <t>1772707239.63658</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2154.922</t>
+          <t>1816916400.9827</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2004.088</t>
+          <t>1663134295.50787</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1948.724</t>
+          <t>1618281909.2813</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2079.913</t>
+          <t>1719084363.22872</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1976.967</t>
+          <t>1638820746.13568</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2080.777</t>
+          <t>1739958568.76811</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>1695.391</t>
+          <t>1695391277.0964</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>39294.519</t>
+          <t>33888671811.6766</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>37790.813</t>
+          <t>32700968045.6508</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>37876.852</t>
+          <t>32657521225.7938</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>41829.607</t>
+          <t>36011331197.9148</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>42897.648</t>
+          <t>37077879069.2573</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>41469.927</t>
+          <t>35676640949.1646</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>42414.751</t>
+          <t>36458734745.8814</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>42665.415</t>
+          <t>37052910842.9012</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>41554.235</t>
+          <t>35728406125.8678</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>39866.455</t>
+          <t>34102984436.2156</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>36193.966</t>
+          <t>31185556906.5971</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>39413.315</t>
+          <t>34007867604.7436</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>36816.269</t>
+          <t>31613827340.7188</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>40453.716</t>
+          <t>35061775959.3565</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>35588.071</t>
+          <t>35588071454.5175</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2973.427</t>
+          <t>2607203589.62694</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3062.561</t>
+          <t>2700452516.3826</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3066.117</t>
+          <t>2689773367.67304</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>3584.796</t>
+          <t>3143112190.0172</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>3530.533</t>
+          <t>3090501307.97031</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>3614.691</t>
+          <t>3157873950.78353</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>3554.276</t>
+          <t>3104815331.69558</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>3453.607</t>
+          <t>3039041258.96821</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>3531.379</t>
+          <t>3082115391.88851</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>3288.097</t>
+          <t>2841511202.21353</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>3051.191</t>
+          <t>2644310052.88844</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2994.603</t>
+          <t>2594430305.92418</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2764.633</t>
+          <t>2387571250.92104</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2508.335</t>
+          <t>2138711755.71891</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2283.121</t>
+          <t>2283121432.91415</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>12516.473</t>
+          <t>11163847174.0565</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>13383.342</t>
+          <t>12008092321.5627</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>14457.356</t>
+          <t>12962481761.6963</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>16185.577</t>
+          <t>14505669622.9611</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>17823.225</t>
+          <t>16037929526.2085</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>18401.433</t>
+          <t>16497025775.5434</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>18660.954</t>
+          <t>16694832740.7444</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>19150.421</t>
+          <t>17253965039.1283</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>19779.129</t>
+          <t>17758424435.9981</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>17652.586</t>
+          <t>15784969213.2318</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>16130.699</t>
+          <t>14336880692.8835</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>16051.174</t>
+          <t>14234825780.7876</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>14095.829</t>
+          <t>12472272409.5526</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>14336.471</t>
+          <t>12757949349.7324</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>13163.097</t>
+          <t>13163096691.9484</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>307.35</t>
+          <t>277805244.420741</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>297.998</t>
+          <t>267402502.581567</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>366.831</t>
+          <t>328878477.714478</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>424.773</t>
+          <t>379093069.271395</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>399.654</t>
+          <t>359364930.104823</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>408.875</t>
+          <t>366483716.593505</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>497.049</t>
+          <t>443847939.114903</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>512.825</t>
+          <t>460386601.477422</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>527.872</t>
+          <t>470599277.327412</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>386.663</t>
+          <t>339557330.72382</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>337.653</t>
+          <t>299099132.03321</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>375.376</t>
+          <t>331346952.372528</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>363.117</t>
+          <t>318730157.016399</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>374.045</t>
+          <t>327125488.404421</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>386.549</t>
+          <t>386549032.59782</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1843.446</t>
+          <t>1613707933.08485</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1832.952</t>
+          <t>1602709486.47235</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1926.017</t>
+          <t>1685992537.49814</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2138.507</t>
+          <t>1864788223.31845</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2274.257</t>
+          <t>1994313635.93987</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2359.41</t>
+          <t>2055367743.98677</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2322.895</t>
+          <t>2016740802.01333</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2327.873</t>
+          <t>2033582342.73132</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2458.297</t>
+          <t>2135450906.64172</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2156.823</t>
+          <t>1863499769.22098</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1942.533</t>
+          <t>1692929409.38368</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1888.515</t>
+          <t>1637498739.28134</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1990.027</t>
+          <t>1722399775.35813</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2029.671</t>
+          <t>1770962712.56302</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>1671.836</t>
+          <t>1671836263.64402</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>26374.426</t>
+          <t>23465407866.1074</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>27086.414</t>
+          <t>24233129834.4923</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>29140.802</t>
+          <t>26008282714.527</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>31916.306</t>
+          <t>28413335801.0957</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>31905.036</t>
+          <t>28486613585.2968</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>31828.395</t>
+          <t>28303133051.8133</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>31006.372</t>
+          <t>27511180158.9348</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>30612.596</t>
+          <t>27318029292.396</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>30091.824</t>
+          <t>26716866994.5138</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>27784.965</t>
+          <t>24494783736.9319</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>24643.317</t>
+          <t>21755702670.05</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>26356.799</t>
+          <t>23239235832.2601</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>24932.529</t>
+          <t>21919553296.2481</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>25623.886</t>
+          <t>22668956401.0309</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>23579.476</t>
+          <t>23579476200.3474</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>29806.385</t>
+          <t>26458533892.2682</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>31923.763</t>
+          <t>28505225172.0937</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>33912.808</t>
+          <t>30241111511.9897</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>34700.381</t>
+          <t>30949569150.1305</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>37716.088</t>
+          <t>33769836690.9974</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>37944.441</t>
+          <t>33803906035.8505</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>38647.625</t>
+          <t>34435322499.6175</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>36096.554</t>
+          <t>32293860116.9613</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>32063.037</t>
+          <t>28505815491.135</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>29155.931</t>
+          <t>25801989816.1215</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>26093.852</t>
+          <t>23044974452.3558</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>25464.028</t>
+          <t>22369811696.5994</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>25821.591</t>
+          <t>22672266698.3564</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>29926.225</t>
+          <t>26516036932.2105</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>22043.443</t>
+          <t>22043443479.8885</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2345.829</t>
+          <t>2138768188.67951</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2317.725</t>
+          <t>2108414273.25415</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2511.769</t>
+          <t>2280294429.36606</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2776.262</t>
+          <t>2529475571.69654</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2895.056</t>
+          <t>2643532928.53352</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>3071.444</t>
+          <t>2796561904.1918</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>3237.878</t>
+          <t>2946457722.42385</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>3316.263</t>
+          <t>3023665505.63076</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>3330.185</t>
+          <t>3023108736.93319</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>3259.905</t>
+          <t>2951533322.91696</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2815.827</t>
+          <t>2538218981.89897</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2629.693</t>
+          <t>2366251370.7924</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2151.981</t>
+          <t>1938120972.19704</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2026.404</t>
+          <t>1824715748.88962</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>1861.17</t>
+          <t>1861170056.5577</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2000.17</t>
+          <t>1669406650.06862</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2045.356</t>
+          <t>1702889171.0742</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2195.624</t>
+          <t>1835238573.00223</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2288.122</t>
+          <t>1908573357.71951</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2134.28</t>
+          <t>1785126651.55139</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2031.616</t>
+          <t>1696922450.8094</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1957.198</t>
+          <t>1644021390.01064</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>1885.088</t>
+          <t>1568937010.97497</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1827.541</t>
+          <t>1520112028.23515</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1729.932</t>
+          <t>1419080680.92557</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1483.592</t>
+          <t>1224563828.06943</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1479.505</t>
+          <t>1234341385.7832</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1395.811</t>
+          <t>1161748867.8502</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1416.784</t>
+          <t>1180762157.58877</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>1310.246</t>
+          <t>1310246087.62473</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>28611.632</t>
+          <t>27575157777.4941</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>30545.224</t>
+          <t>29548550512.5372</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>31218.443</t>
+          <t>30066084698.7405</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>36251.097</t>
+          <t>34848508765.0787</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>37035.301</t>
+          <t>35478585921.3444</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>34797.984</t>
+          <t>33316661823.1808</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>33163.643</t>
+          <t>30719682192.146</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>34000.298</t>
+          <t>31404444564.1026</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>33261.233</t>
+          <t>30617328129.4136</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>36183.199</t>
+          <t>33255333760.0346</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>37114.124</t>
+          <t>34172408853.7489</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>37749.556</t>
+          <t>34688052631.0881</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>40595.486</t>
+          <t>37312414348.619</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>43946.903</t>
+          <t>40629534424.4848</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>45140.355</t>
+          <t>45140354856.6739</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>189570.321</t>
+          <t>180723894687.524</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>187155.714</t>
+          <t>178777896974.411</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>186671.186</t>
+          <t>178621832550.175</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>187705.421</t>
+          <t>179399936316.026</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>184930.821</t>
+          <t>177238967022.934</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>186868.916</t>
+          <t>179382310179.335</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>185021.452</t>
+          <t>177743881235.775</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>189025.774</t>
+          <t>180960663434.701</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>186711.658</t>
+          <t>178732095721.187</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>191182.623</t>
+          <t>182254931702.034</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>187841.283</t>
+          <t>179070902784.296</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>192533.713</t>
+          <t>183264378130.96</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>209722.628</t>
+          <t>198055985326.678</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>229190.16</t>
+          <t>216570583804.988</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>230929.681</t>
+          <t>230929680935.897</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1166.896</t>
+          <t>1048884396.19534</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1430.469</t>
+          <t>1287750482.22365</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1526.727</t>
+          <t>1367035279.05852</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1531.221</t>
+          <t>1363797884.97533</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1797.951</t>
+          <t>1611157692.61184</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2003.033</t>
+          <t>1785662199.9489</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2136.371</t>
+          <t>1897756801.10736</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2132.746</t>
+          <t>1906580242.90069</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2098.786</t>
+          <t>1868318348.15367</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>1612.838</t>
+          <t>1403838448.87262</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>998.967</t>
+          <t>869631405.132415</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1384.326</t>
+          <t>1202162660.54825</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1296.773</t>
+          <t>1124813596.73393</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>1349.449</t>
+          <t>1174644670.80733</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>1093.346</t>
+          <t>1093345958.51722</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>15351.52</t>
+          <t>13409927817.408</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>15928.62</t>
+          <t>13997149619.1908</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>16736.968</t>
+          <t>14679584471.1542</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>18395.495</t>
+          <t>16114273547.4315</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>19714.664</t>
+          <t>17331120501.1135</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>19816.589</t>
+          <t>17355927831.2647</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>20854.002</t>
+          <t>18248281945.5305</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>19761.707</t>
+          <t>17371098924.7114</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>20000.757</t>
+          <t>17477202017.4741</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>17937.845</t>
+          <t>15531483961.2492</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>17081.58</t>
+          <t>14827749993.3488</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>17456.839</t>
+          <t>15145229598.6729</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>15360.157</t>
+          <t>13265176877.9423</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>14944.659</t>
+          <t>12971702573.39</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>13269.447</t>
+          <t>13269447219.2578</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>77077.223</t>
+          <t>65613483559.0612</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>73233.861</t>
+          <t>62432230240.8222</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>69695.882</t>
+          <t>58954093461.8254</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>71824.384</t>
+          <t>60664891377.4831</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>74127.439</t>
+          <t>63039232074.5609</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>73773.413</t>
+          <t>62616572026.5695</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>72118.043</t>
+          <t>61229400106.4911</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>63347.16</t>
+          <t>54076015695.9084</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>61627.266</t>
+          <t>51980038791.6894</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>59067.759</t>
+          <t>48302013441.7378</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>57496.765</t>
+          <t>47008898045.2253</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>62840.317</t>
+          <t>50973399836.3294</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>60662.938</t>
+          <t>49132314808.9106</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>56356.386</t>
+          <t>46381947523.5308</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>45742.063</t>
+          <t>45742062905.3531</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>14056.78</t>
+          <t>12397457558.5172</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>14693.85</t>
+          <t>13002887590.9366</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>15642.221</t>
+          <t>13808907436.5382</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>17031.544</t>
+          <t>15045526680.244</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>18617.998</t>
+          <t>16413579133.0527</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>18464.343</t>
+          <t>16081850250.738</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>18973.815</t>
+          <t>16522209708.4924</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>18067.891</t>
+          <t>15836520232.9218</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>17720.439</t>
+          <t>15459540916.8292</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>17649.456</t>
+          <t>15407934853.2945</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>17896.431</t>
+          <t>15711792781.2981</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>19493.293</t>
+          <t>16924723373.5361</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>20632.27</t>
+          <t>17941616291.0957</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>22159.576</t>
+          <t>19352589300.3644</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>19889.895</t>
+          <t>19889894746.653</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>847.595</t>
+          <t>739808731.849372</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>834.18</t>
+          <t>740448355.717965</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>898.127</t>
+          <t>797152161.718218</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>989.962</t>
+          <t>882124770.040954</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>911.935</t>
+          <t>814344849.699431</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>935.911</t>
+          <t>833462670.731432</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1051.476</t>
+          <t>938809794.433449</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>997.946</t>
+          <t>896574126.86273</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1059.732</t>
+          <t>950555071.636451</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>865.654</t>
+          <t>758483156.18543</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>710.819</t>
+          <t>628155575.357833</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>785.044</t>
+          <t>697064770.306872</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>772.54</t>
+          <t>685621120.22399</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>843.691</t>
+          <t>752778915.539511</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>812.061</t>
+          <t>812061343.203838</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>261.394</t>
+          <t>224251235.538105</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>272.463</t>
+          <t>235931472.329628</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>296.137</t>
+          <t>255719415.495814</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>314.086</t>
+          <t>268907718.016566</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>339.314</t>
+          <t>289067707.876644</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>367.543</t>
+          <t>311085998.361418</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>396.722</t>
+          <t>337750229.983374</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>374.642</t>
+          <t>317517942.341822</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>489.54</t>
+          <t>421259655.136559</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>542.595</t>
+          <t>465260221.777327</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>532.045</t>
+          <t>460103061.08995</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>562.602</t>
+          <t>484619155.556489</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>520.471</t>
+          <t>446060034.810851</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>530.325</t>
+          <t>453230147.872765</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>495.502</t>
+          <t>495502432.675888</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>576.972</t>
+          <t>502298113.947982</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>587.41</t>
+          <t>522513093.592771</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>578.206</t>
+          <t>519482441.418896</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>620.21</t>
+          <t>555588381.574627</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>599.238</t>
+          <t>538630327.490354</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>625.266</t>
+          <t>558112098.828598</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>730.118</t>
+          <t>650202346.124843</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>798.811</t>
+          <t>709695975.516289</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>796.407</t>
+          <t>705430275.80751</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>568.084</t>
+          <t>496375643.829363</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>436.132</t>
+          <t>382138506.608908</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>458.665</t>
+          <t>401125712.900103</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>467.138</t>
+          <t>408792753.602851</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>470.786</t>
+          <t>414005979.162035</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>458.546</t>
+          <t>458546206.76313</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>10919.16</t>
+          <t>10004420369.4901</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>11627.375</t>
+          <t>10637505762.8771</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>12162.978</t>
+          <t>11097322500.5604</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>11911.637</t>
+          <t>10902825150.9171</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>11548.954</t>
+          <t>10623401262.0544</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>11569.028</t>
+          <t>10620577891.0359</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>11675.046</t>
+          <t>10718925443.4486</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>11729.112</t>
+          <t>10800918578.9417</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>11306.196</t>
+          <t>10384500900.0405</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>11035.66</t>
+          <t>10136058858.2956</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>10968.666</t>
+          <t>10107450535.0638</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>10930.083</t>
+          <t>10035313889.2292</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>11163.307</t>
+          <t>10292694430.6513</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>11403.232</t>
+          <t>10538139676.7632</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>10547.373</t>
+          <t>10547372504.6083</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>106.605</t>
+          <t>93604714.8938171</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>110.268</t>
+          <t>97156894.4108067</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>115.958</t>
+          <t>102864304.995023</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>136.538</t>
+          <t>119674681.306513</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>128.633</t>
+          <t>113925797.848307</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>142.325</t>
+          <t>125542655.108792</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>138.181</t>
+          <t>121376299.543031</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>134.832</t>
+          <t>119022573.974513</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>153.437</t>
+          <t>134513688.401028</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>140.303</t>
+          <t>120321697.179246</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>131.327</t>
+          <t>113840365.297953</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>133.993</t>
+          <t>114873673.980351</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>137.328</t>
+          <t>117619868.197013</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>138.998</t>
+          <t>119059804.008912</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>116.749</t>
+          <t>116748942.765175</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>13308.088</t>
+          <t>11875263150.7137</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>12872.534</t>
+          <t>11567389160.9876</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>13394.602</t>
+          <t>11944116903.1223</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>12614.339</t>
+          <t>11194285281.798</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>12047.589</t>
+          <t>10736465756.0353</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>11486.499</t>
+          <t>10199179952.6288</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>11690.256</t>
+          <t>10366254041.3694</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>12160.664</t>
+          <t>10852127025.2017</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>13033.611</t>
+          <t>11590931743.0141</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>11512.044</t>
+          <t>10073236052.3529</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>9311.557</t>
+          <t>8144700546.86019</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>9208.593</t>
+          <t>8025713003.33579</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>8648.76</t>
+          <t>7504001254.0165</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>12158.885</t>
+          <t>10606852229.5414</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>10599.574</t>
+          <t>10599573804.119</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>7353.776</t>
+          <t>6863303948.33116</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8041.786</t>
+          <t>7574025493.09027</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>6943.59</t>
+          <t>6512070481.56544</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>6686.971</t>
+          <t>6257750237.89409</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>6462.394</t>
+          <t>6051590514.68034</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>6604.295</t>
+          <t>6158615227.84328</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>6682.947</t>
+          <t>6205100704.79645</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>6998.978</t>
+          <t>6496423800.04264</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>7844.64</t>
+          <t>7238245655.25849</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>7085.288</t>
+          <t>6527097807.36099</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>7172.008</t>
+          <t>6588461604.903</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>7276.904</t>
+          <t>6668194634.85703</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>7012.765</t>
+          <t>6425520575.61601</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>7263.445</t>
+          <t>6645990249.41018</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>6799.49</t>
+          <t>6799490083.96442</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3849.499</t>
+          <t>3456511041.22145</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3943.755</t>
+          <t>3567080703.40906</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>3847.008</t>
+          <t>3455446463.04891</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>3960.701</t>
+          <t>3544885477.07974</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>4017.096</t>
+          <t>3603911501.57679</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>3941.184</t>
+          <t>3529165180.61434</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>3777.037</t>
+          <t>3368737982.1922</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>3670.828</t>
+          <t>3280686072.2708</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>3732.273</t>
+          <t>3317345872.41792</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>3378.896</t>
+          <t>2983889996.84319</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>3217.864</t>
+          <t>2848172668.98791</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>3276.147</t>
+          <t>2891693529.44417</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>3018.827</t>
+          <t>2660232743.58568</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>3009.971</t>
+          <t>2667183851.0964</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2625.775</t>
+          <t>2625775001.22659</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>7162.892</t>
+          <t>6174472831.20049</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>7144.284</t>
+          <t>6157287056.56833</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>5638.239</t>
+          <t>4856457661.32649</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>5804.915</t>
+          <t>5035496794.35851</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>5264.464</t>
+          <t>4633206728.47967</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>6006.876</t>
+          <t>5294327973.6181</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>6063.294</t>
+          <t>5386804676.00504</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>6156.993</t>
+          <t>5475602059.52053</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>6405.77</t>
+          <t>5676115535.63847</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>5781.094</t>
+          <t>5094036431.18032</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>5339.744</t>
+          <t>4788937219.04966</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>4887.364</t>
+          <t>4364132466.76988</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>3600.267</t>
+          <t>3166593748.05854</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>3409.842</t>
+          <t>3001052497.51873</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>3270.29</t>
+          <t>3270290071.93774</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>44599.48</t>
+          <t>41187372885.6237</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>44759.562</t>
+          <t>41435317474.878</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>46820.961</t>
+          <t>43025620881.5693</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>50946.889</t>
+          <t>46581191141.5971</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>53930.817</t>
+          <t>50413656546.5066</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>56402.903</t>
+          <t>51829887835.7212</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>57320.655</t>
+          <t>52706226914.3718</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>62611.907</t>
+          <t>58325869064.0101</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>59015.029</t>
+          <t>54681750036.2788</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>59649.838</t>
+          <t>55292254318.0857</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>64364.412</t>
+          <t>59666583566.8627</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>63396.06</t>
+          <t>58515139471.5882</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>69798.126</t>
+          <t>64405749672.7687</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>69422.697</t>
+          <t>64050740419.7961</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>55170.293</t>
+          <t>55170293037.8801</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>887.386</t>
+          <t>747015759.186418</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>845.848</t>
+          <t>709258567.901577</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>861.379</t>
+          <t>721972838.256093</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>899.436</t>
+          <t>754298528.394552</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1090.206</t>
+          <t>928869858.141477</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1149.28</t>
+          <t>969879685.438794</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>1268.892</t>
+          <t>1076349426.81968</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>1511.945</t>
+          <t>1302860586.85628</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>1446.023</t>
+          <t>1235978017.69484</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>1593.293</t>
+          <t>1350166214.68035</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1371.351</t>
+          <t>1158243429.69579</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1428.982</t>
+          <t>1198167719.6197</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1531.233</t>
+          <t>1300794008.20371</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>1608.591</t>
+          <t>1370368220.7426</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>1392.16</t>
+          <t>1392159795.52958</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>730.654</t>
+          <t>645211397.370462</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>746.326</t>
+          <t>659687500.9277</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>753.734</t>
+          <t>666598399.959995</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>839.508</t>
+          <t>744745115.07258</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>985.667</t>
+          <t>875298211.002777</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1008.668</t>
+          <t>893432957.885647</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1025.488</t>
+          <t>909370594.534995</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>1030.161</t>
+          <t>918899213.411196</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1066.694</t>
+          <t>945368714.140154</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1066.353</t>
+          <t>935807439.886879</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>969.128</t>
+          <t>855811561.345628</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1003.47</t>
+          <t>885123962.495499</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>953.598</t>
+          <t>839994679.694612</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>934.724</t>
+          <t>824650585.178988</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>837.208</t>
+          <t>837208249.870978</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4083.848</t>
+          <t>3566462086.90816</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4076.103</t>
+          <t>3583394075.39151</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>4166.124</t>
+          <t>3655658203.06033</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>4430.687</t>
+          <t>3874142963.08788</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>4708.223</t>
+          <t>4129071132.85538</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>4586.277</t>
+          <t>4003302176.80594</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>4581.653</t>
+          <t>3984046720.75958</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>4554.149</t>
+          <t>3983174773.04794</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>4561.278</t>
+          <t>3962722422.15929</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>4132.208</t>
+          <t>3566389084.30284</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>3795.893</t>
+          <t>3271998008.89845</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>4299.671</t>
+          <t>3711731350.49528</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>4042.077</t>
+          <t>3473874209.29322</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>4300.948</t>
+          <t>3701848735.5306</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>3695.881</t>
+          <t>3695880739.29312</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>8747.095</t>
+          <t>7984518158.11916</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>8408.936</t>
+          <t>7765255869.06021</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>7531.582</t>
+          <t>6973313085.01473</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>7698.138</t>
+          <t>7090114467.33463</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>8283.161</t>
+          <t>7589809077.50995</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>8050.893</t>
+          <t>7278954118.86172</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>7760.331</t>
+          <t>6947731965.77505</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>7698.165</t>
+          <t>6867803138.71299</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>7757.295</t>
+          <t>6827047101.6151</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>7211.382</t>
+          <t>6265487810.64662</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>8012.093</t>
+          <t>7070802327.98043</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>8769.952</t>
+          <t>7757031440.18528</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>9047.748</t>
+          <t>8018309620.392</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>9399.615</t>
+          <t>8340668009.79253</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>9079.63</t>
+          <t>9079629787.32877</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>12095.022</t>
+          <t>10780717674.0855</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>11602.969</t>
+          <t>10367090661.6016</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>12141.184</t>
+          <t>10778884629.5732</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>12565.577</t>
+          <t>11127525839.8045</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>12839.887</t>
+          <t>11374760760.72</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>12885.79</t>
+          <t>11344418858.5308</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>12786.862</t>
+          <t>11250984312.7903</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>12125.91</t>
+          <t>10794941479.8897</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>11653.859</t>
+          <t>10382556073.5253</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>11075.042</t>
+          <t>9837274038.85605</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>11448.859</t>
+          <t>10258288116.8191</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>11542.618</t>
+          <t>10285508979.5351</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>11305.473</t>
+          <t>10052335439.812</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>10741.856</t>
+          <t>9527854155.24815</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>10279.233</t>
+          <t>10279232560.6949</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>159922.399</t>
+          <t>141224321150.187</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>163183.912</t>
+          <t>144670333162.606</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>168288.379</t>
+          <t>148697637461.773</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>171437.537</t>
+          <t>151688098675.757</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>174461.439</t>
+          <t>154523640989.314</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>178350.677</t>
+          <t>157071849972.081</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>176717.382</t>
+          <t>154784067402.218</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>164294.24</t>
+          <t>144232731969.459</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>153797.292</t>
+          <t>134113184025.187</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>140905.354</t>
+          <t>122138153171.296</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>136682.053</t>
+          <t>118287849803.04</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>139060.172</t>
+          <t>119712743528.617</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>141892.873</t>
+          <t>122268490836.398</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>139721.128</t>
+          <t>122033401386.493</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>124594.627</t>
+          <t>124594626817.757</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>784145.643</t>
+          <t>701969528910.809</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>793783.161</t>
+          <t>716439369360.815</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>843291.321</t>
+          <t>755371211833.954</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>852325.494</t>
+          <t>765278712031.646</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>835279.28</t>
+          <t>755518961195.769</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>865014.563</t>
+          <t>778125584741.522</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>892263.011</t>
+          <t>802491404536.551</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>860580.123</t>
+          <t>784852149824.133</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>871091.336</t>
+          <t>793867448372.563</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>884945.85</t>
+          <t>807783895867.936</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>863456.849</t>
+          <t>789815941783.074</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>863065.165</t>
+          <t>788953674307.562</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>915735.237</t>
+          <t>840808363837.985</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>948179.837</t>
+          <t>880081122460.16</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>910391.408</t>
+          <t>910391408287.323</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2084936.279</t>
+          <t>1882079802952.11</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2102073.868</t>
+          <t>1909278574784.17</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2182191.487</t>
+          <t>1976363096510.35</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2208467.068</t>
+          <t>2001964832381.4</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2209677.18</t>
+          <t>2012269218370.98</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2229823.532</t>
+          <t>2021616707179.41</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2265198.756</t>
+          <t>2053390232294.72</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2204421.855</t>
+          <t>2015933976872.98</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2242645.991</t>
+          <t>2044312200204.19</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2267177.05</t>
+          <t>2061475200731.67</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2223712.328</t>
+          <t>2026855784387.96</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>2282378.811</t>
+          <t>2073329108909.64</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>2388280.219</t>
+          <t>2169699830787.39</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2435136.303</t>
+          <t>2225351236304.94</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2270420.724</t>
+          <t>2270420724174.59</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4337,84 +4342,84 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1063.52</t>
+          <t>959420396.661889</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>997.039</t>
+          <t>899672160.633213</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>1103.116</t>
+          <t>990687435.155987</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1129.992</t>
+          <t>1015071772.5007</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1232.457</t>
+          <t>1108548495.16276</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1259.359</t>
+          <t>1131780926.60717</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>1319.459</t>
+          <t>1182660132.61563</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>1388.279</t>
+          <t>1254136557.87557</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>1486.963</t>
+          <t>1334166442.55047</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>1394.057</t>
+          <t>1238601224.47945</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1270.214</t>
+          <t>1129432247.94145</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1199.064</t>
+          <t>1064151080.39283</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1104.751</t>
+          <t>979970077.351811</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>1004.792</t>
+          <t>888859391.55146</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>833.975</t>
+          <t>833974684.972356</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4424,84 +4429,84 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4786.923</t>
+          <t>4116811699.80754</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>4654.408</t>
+          <t>4019557832.30607</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>4707.963</t>
+          <t>4057082749.99276</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>5006.151</t>
+          <t>4325747819.60452</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>4808.478</t>
+          <t>4169426797.69074</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>4788.055</t>
+          <t>4122148834.75073</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>4810.139</t>
+          <t>4146011461.41684</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>4632.177</t>
+          <t>4016016454.99168</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>4837.716</t>
+          <t>4176749800.78725</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>4595.27</t>
+          <t>3910871090.73012</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>4652.214</t>
+          <t>3964539912.68512</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>5150.7</t>
+          <t>4364882069.26363</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>5075.758</t>
+          <t>4289221154.2796</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>5332.645</t>
+          <t>4559933628.10334</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>4582.79</t>
+          <t>4582790218.46574</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4511,84 +4516,84 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2741.309</t>
+          <t>2330374910.32266</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2859.475</t>
+          <t>2471799824.57533</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>3000.298</t>
+          <t>2595262062.55103</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>3066.857</t>
+          <t>2646375242.59014</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>3298.455</t>
+          <t>2893750567.54376</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>3304.827</t>
+          <t>2872116573.09089</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>3450.037</t>
+          <t>3003212809.95938</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>3610.65</t>
+          <t>3168251625.54171</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>3688.957</t>
+          <t>3202180208.36056</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>3548.203</t>
+          <t>3049455571.45788</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>3223.105</t>
+          <t>2768171939.55112</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>3616.979</t>
+          <t>3094438852.94785</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>3360.782</t>
+          <t>2884791728.05203</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>3735.256</t>
+          <t>3233550536.47227</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>3286.095</t>
+          <t>3286094748.10312</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4600,7 +4605,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4612,7 +4617,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4624,7 +4629,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4636,7 +4641,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4648,7 +4653,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4695,6 +4700,11 @@
           <t>labour_force_value.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4729,6 +4739,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
